--- a/Assignments/hw18-VC ProblemSets & CEO of Pickle/VC Problem Set.xlsx
+++ b/Assignments/hw18-VC ProblemSets & CEO of Pickle/VC Problem Set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gloria/Desktop/UPenn/_EAS 5450/ASSIGNMENTS/#18/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\#MS\SP25\EAS5450-Eng_Entrepreneurship\Assignments\hw18-VC ProblemSets &amp; CEO of Pickle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D9B302-60E6-5648-A806-10DC06C0BEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F1D1B8-8A81-424B-8728-EF949081EBDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4540" yWindow="500" windowWidth="27220" windowHeight="16940" activeTab="3" xr2:uid="{1D240600-3BEC-6A44-AB40-F1617F70031E}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="16629" windowHeight="17880" activeTab="1" xr2:uid="{1D240600-3BEC-6A44-AB40-F1617F70031E}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="2" r:id="rId1"/>
@@ -335,20 +335,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="[$$-409]#,##0"/>
-    <numFmt numFmtId="169" formatCode="[$$-409]#,##0.000"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="181" formatCode="[$$-409]#,##0"/>
+    <numFmt numFmtId="182" formatCode="[$$-409]#,##0.000"/>
+    <numFmt numFmtId="183" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -360,7 +360,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -451,6 +451,13 @@
       <color theme="5"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -544,19 +551,19 @@
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -564,13 +571,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -592,24 +599,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="6" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="6" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -620,29 +627,29 @@
     <xf numFmtId="9" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -651,12 +658,12 @@
     <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -667,7 +674,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -676,53 +683,52 @@
     <xf numFmtId="10" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="15" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="182" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{7FF074B8-B4DB-A14B-A0C6-892F1D0DFFC0}"/>
     <cellStyle name="Currency 2" xfId="2" xr:uid="{E776F6C1-3942-774F-9B5F-B2371EC6F4E8}"/>
     <cellStyle name="Currency 3" xfId="6" xr:uid="{EFB5969F-CA19-CD49-94FA-9766046714BF}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{96BC802C-848D-2340-8005-6E3137C989E5}"/>
     <cellStyle name="Normal 3" xfId="5" xr:uid="{17B1A740-F181-9242-B943-607806BFBAD8}"/>
     <cellStyle name="Percent 2" xfId="4" xr:uid="{6AC55666-4640-6443-8058-D8180A3EB4A2}"/>
     <cellStyle name="Percent 3" xfId="7" xr:uid="{73396071-09AB-654D-88D6-C278604EB0DE}"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4253,8 +4259,8 @@
       <xdr:row>49</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -4583,7 +4589,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="TextBox 15">
@@ -7526,7 +7532,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -7846,22 +7852,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="19.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.83203125" style="5"/>
+    <col min="1" max="1" width="24.46484375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="19.46484375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.46484375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.46484375" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.46484375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
     </row>
-    <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="16.75" x14ac:dyDescent="0.65">
       <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
@@ -7877,7 +7883,7 @@
       <c r="E2" s="8"/>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
@@ -7894,7 +7900,7 @@
       <c r="E3" s="16"/>
       <c r="G3" s="16"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
@@ -7911,7 +7917,7 @@
       <c r="E4" s="16"/>
       <c r="G4" s="16"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
@@ -7928,7 +7934,7 @@
       <c r="E5" s="16"/>
       <c r="G5" s="16"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
@@ -7942,12 +7948,12 @@
       </c>
       <c r="D6" s="9"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>1</v>
       </c>
@@ -7958,39 +7964,39 @@
       <c r="E9" s="18"/>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>20</v>
       </c>
@@ -8004,7 +8010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>32</v>
       </c>
@@ -8020,7 +8026,7 @@
       <c r="E18" s="18"/>
       <c r="G18" s="18"/>
     </row>
-    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:7" ht="42.45" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
         <v>21</v>
       </c>
@@ -8036,7 +8042,7 @@
       <c r="E19" s="18"/>
       <c r="G19" s="18"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>31</v>
       </c>
@@ -8052,7 +8058,7 @@
       <c r="E20" s="12"/>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>17</v>
       </c>
@@ -8069,19 +8075,19 @@
       <c r="E21" s="18"/>
       <c r="G21" s="18"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B22" s="19"/>
       <c r="C22" s="18"/>
       <c r="E22" s="18"/>
       <c r="G22" s="18"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="11"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>29</v>
       </c>
@@ -8089,7 +8095,7 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>30</v>
       </c>
@@ -8098,7 +8104,7 @@
         <v>65000000</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>27</v>
       </c>
@@ -8106,12 +8112,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="84" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -8120,20 +8127,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B309F835-626D-2940-8045-5565D1665218}">
   <dimension ref="A8:P71"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="33.5" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.46484375" style="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" style="26" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1328125" style="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.5" style="26" customWidth="1"/>
-    <col min="7" max="7" width="28.1640625" style="26" customWidth="1"/>
+    <col min="6" max="6" width="28.46484375" style="26" customWidth="1"/>
+    <col min="7" max="7" width="28.1328125" style="26" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="26"/>
+    <col min="9" max="16384" width="10.796875" style="26"/>
   </cols>
   <sheetData>
-    <row r="8" spans="1:9" s="31" customFormat="1" ht="19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A8" s="55" t="s">
         <v>14</v>
       </c>
@@ -8152,7 +8159,7 @@
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
     </row>
-    <row r="9" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="32" t="s">
         <v>7</v>
       </c>
@@ -8173,7 +8180,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="32" t="s">
         <v>8</v>
       </c>
@@ -8194,7 +8201,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A11" s="32" t="s">
         <v>9</v>
       </c>
@@ -8215,7 +8222,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A12" s="32" t="s">
         <v>5</v>
       </c>
@@ -8235,7 +8242,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3"/>
       <c r="D13" s="4"/>
       <c r="F13" s="33" t="s">
@@ -8246,7 +8253,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="34" t="s">
         <v>26</v>
       </c>
@@ -8262,7 +8269,7 @@
       <c r="H14" s="31"/>
       <c r="I14" s="31"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="41" t="s">
         <v>29</v>
       </c>
@@ -8280,7 +8287,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="42" t="s">
         <v>30</v>
       </c>
@@ -8295,7 +8302,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17" s="42" t="s">
         <v>27</v>
       </c>
@@ -8310,7 +8317,7 @@
         <v>55555.555555555562</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18" s="35" t="s">
         <v>28</v>
       </c>
@@ -8326,12 +8333,12 @@
         <v>7.1999999999999993</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="22.3" x14ac:dyDescent="0.5">
       <c r="A20" s="81" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21" s="30" t="s">
         <v>25</v>
       </c>
@@ -8351,7 +8358,7 @@
       <c r="O21" s="31"/>
       <c r="P21" s="31"/>
     </row>
-    <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="57" t="s">
         <v>20</v>
       </c>
@@ -8379,7 +8386,7 @@
       <c r="O22" s="31"/>
       <c r="P22" s="31"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23" s="33" t="s">
         <v>32</v>
       </c>
@@ -8408,7 +8415,7 @@
       <c r="O23" s="31"/>
       <c r="P23" s="31"/>
     </row>
-    <row r="24" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" ht="46.3" x14ac:dyDescent="0.4">
       <c r="A24" s="37" t="s">
         <v>21</v>
       </c>
@@ -8436,7 +8443,7 @@
       <c r="O24" s="31"/>
       <c r="P24" s="31"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25" s="33" t="s">
         <v>31</v>
       </c>
@@ -8464,7 +8471,7 @@
       <c r="O25" s="31"/>
       <c r="P25" s="31"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26" s="33" t="s">
         <v>33</v>
       </c>
@@ -8493,7 +8500,7 @@
       <c r="O26" s="31"/>
       <c r="P26" s="31"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27" s="33" t="s">
         <v>34</v>
       </c>
@@ -8513,7 +8520,7 @@
         <v>14365000.000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
         <v>75</v>
       </c>
@@ -8533,7 +8540,7 @@
         <v>0.15785714285714289</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29" s="29" t="s">
         <v>39</v>
       </c>
@@ -8553,7 +8560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30" s="78" t="s">
         <v>40</v>
       </c>
@@ -8574,7 +8581,7 @@
         <v>0.15785714285714289</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
         <v>55</v>
       </c>
@@ -8597,7 +8604,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32" s="29" t="s">
         <v>57</v>
       </c>
@@ -8617,7 +8624,7 @@
         <v>54.480917159763294</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="78" t="s">
         <v>56</v>
       </c>
@@ -8639,7 +8646,7 @@
       </c>
       <c r="F33" s="27"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="78" t="s">
         <v>58</v>
       </c>
@@ -8661,7 +8668,7 @@
       </c>
       <c r="F34" s="27"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="78" t="s">
         <v>38</v>
       </c>
@@ -8682,7 +8689,7 @@
         <v>53846153.846153833</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="78" t="s">
         <v>37</v>
       </c>
@@ -8703,7 +8710,7 @@
         <v>45346153.846153833</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="29" t="s">
         <v>61</v>
       </c>
@@ -8712,7 +8719,7 @@
         <v>1098165.4301746294</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="29" t="s">
         <v>59</v>
       </c>
@@ -8721,7 +8728,7 @@
         <v>82.865475000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="29" t="s">
         <v>60</v>
       </c>
@@ -8739,22 +8746,22 @@
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="22.3" x14ac:dyDescent="0.5">
       <c r="A49" s="81" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A50" s="34" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A51" s="26" t="s">
         <v>67</v>
       </c>
@@ -8762,7 +8769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A52" s="55" t="s">
         <v>66</v>
       </c>
@@ -8780,7 +8787,7 @@
       </c>
       <c r="I52" s="44"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" s="32" t="s">
         <v>7</v>
       </c>
@@ -8799,7 +8806,7 @@
         <v>2.1445130562986927</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="32" t="s">
         <v>8</v>
       </c>
@@ -8818,7 +8825,7 @@
         <v>1.9212752636103287</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A55" s="32" t="s">
         <v>9</v>
       </c>
@@ -8837,7 +8844,7 @@
         <v>1.9212752636103287</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="32" t="s">
         <v>63</v>
       </c>
@@ -8857,12 +8864,12 @@
         <v>0.50258894041249391</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="22.3" x14ac:dyDescent="0.5">
       <c r="A65" s="81" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A66" s="41" t="s">
         <v>32</v>
       </c>
@@ -8870,7 +8877,7 @@
         <v>17000000</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A67" s="42" t="s">
         <v>72</v>
       </c>
@@ -8878,7 +8885,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A68" s="42" t="s">
         <v>73</v>
       </c>
@@ -8886,7 +8893,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A69" s="35" t="s">
         <v>34</v>
       </c>
@@ -8895,7 +8902,7 @@
         <v>129093750</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A70" s="29" t="s">
         <v>74</v>
       </c>
@@ -8904,7 +8911,7 @@
         <v>91000000</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A71" s="29" t="s">
         <v>75</v>
       </c>
@@ -8917,6 +8924,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -8925,21 +8933,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD4B13C9-9D0E-1B40-AE81-E9FFAFAD317A}">
   <dimension ref="A7:Q50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="33.5" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.46484375" style="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" style="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1328125" style="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.33203125" style="26" customWidth="1"/>
-    <col min="7" max="7" width="28.5" style="26" customWidth="1"/>
-    <col min="8" max="8" width="28.1640625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="28.46484375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="28.1328125" style="26" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="26"/>
+    <col min="10" max="16384" width="10.796875" style="26"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:10" s="31" customFormat="1" ht="19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" s="31" customFormat="1" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A7" s="55" t="s">
         <v>14</v>
       </c>
@@ -8958,7 +8966,7 @@
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
     </row>
-    <row r="8" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="32" t="s">
         <v>7</v>
       </c>
@@ -8979,7 +8987,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="32" t="s">
         <v>8</v>
       </c>
@@ -9000,7 +9008,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="32" t="s">
         <v>9</v>
       </c>
@@ -9021,7 +9029,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A11" s="32" t="s">
         <v>5</v>
       </c>
@@ -9041,7 +9049,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
       <c r="G12" s="33" t="s">
@@ -9052,7 +9060,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="34" t="s">
         <v>26</v>
       </c>
@@ -9068,7 +9076,7 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="41" t="s">
         <v>29</v>
       </c>
@@ -9086,7 +9094,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="42" t="s">
         <v>30</v>
       </c>
@@ -9101,7 +9109,7 @@
         <v>0.10279500898504523</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="42" t="s">
         <v>27</v>
       </c>
@@ -9116,7 +9124,7 @@
         <v>57286.244511836332</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="35" t="s">
         <v>28</v>
       </c>
@@ -9132,12 +9140,12 @@
         <v>6.9824790123456788</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="22.3" x14ac:dyDescent="0.5">
       <c r="A19" s="81" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A20" s="30" t="s">
         <v>78</v>
       </c>
@@ -9160,7 +9168,7 @@
       <c r="P20" s="31"/>
       <c r="Q20" s="31"/>
     </row>
-    <row r="21" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="57" t="s">
         <v>20</v>
       </c>
@@ -9191,7 +9199,7 @@
       <c r="P21" s="31"/>
       <c r="Q21" s="31"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="33" t="s">
         <v>32</v>
       </c>
@@ -9223,7 +9231,7 @@
       <c r="P22" s="31"/>
       <c r="Q22" s="31"/>
     </row>
-    <row r="23" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="46.3" x14ac:dyDescent="0.4">
       <c r="A23" s="37" t="s">
         <v>21</v>
       </c>
@@ -9254,7 +9262,7 @@
       <c r="P23" s="31"/>
       <c r="Q23" s="31"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="33" t="s">
         <v>31</v>
       </c>
@@ -9285,7 +9293,7 @@
       <c r="P24" s="31"/>
       <c r="Q24" s="31"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A25" s="33" t="s">
         <v>33</v>
       </c>
@@ -9317,7 +9325,7 @@
       <c r="P25" s="31"/>
       <c r="Q25" s="31"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="33" t="s">
         <v>34</v>
       </c>
@@ -9340,7 +9348,7 @@
         <v>14365000.000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="78" t="s">
         <v>76</v>
       </c>
@@ -9363,7 +9371,7 @@
         <v>0.15785714285714289</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
         <v>77</v>
       </c>
@@ -9384,7 +9392,7 @@
         <v>0.1420714285714286</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="29" t="s">
         <v>39</v>
       </c>
@@ -9407,7 +9415,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="78" t="s">
         <v>40</v>
       </c>
@@ -9431,7 +9439,7 @@
         <v>0.17539682539682544</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
         <v>55</v>
       </c>
@@ -9458,7 +9466,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="29" t="s">
         <v>57</v>
       </c>
@@ -9482,7 +9490,7 @@
         <v>43.711686390532535</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A33" s="78" t="s">
         <v>56</v>
       </c>
@@ -9508,7 +9516,7 @@
       </c>
       <c r="G33" s="27"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A34" s="78" t="s">
         <v>58</v>
       </c>
@@ -9534,7 +9542,7 @@
       </c>
       <c r="G34" s="27"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A35" s="78" t="s">
         <v>38</v>
       </c>
@@ -9559,7 +9567,7 @@
         <v>48461538.461538449</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A36" s="78" t="s">
         <v>37</v>
       </c>
@@ -9584,7 +9592,7 @@
         <v>39961538.461538449</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A39" s="29" t="s">
         <v>61</v>
       </c>
@@ -9593,7 +9601,7 @@
         <v>1372983.9013865627</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A40" s="29" t="s">
         <v>59</v>
       </c>
@@ -9602,7 +9610,7 @@
         <v>66.279000000000011</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A41" s="29" t="s">
         <v>60</v>
       </c>
@@ -9621,17 +9629,17 @@
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A42" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A44" s="34" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A45" s="26" t="s">
         <v>67</v>
       </c>
@@ -9639,7 +9647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A46" s="55" t="s">
         <v>66</v>
       </c>
@@ -9658,7 +9666,7 @@
       <c r="F46" s="98"/>
       <c r="J46" s="44"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A47" s="32" t="s">
         <v>7</v>
       </c>
@@ -9678,7 +9686,7 @@
       </c>
       <c r="F47" s="99"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A48" s="32" t="s">
         <v>8</v>
       </c>
@@ -9701,7 +9709,7 @@
         <v>9941850.0000000019</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="32" t="s">
         <v>9</v>
       </c>
@@ -9721,7 +9729,7 @@
       </c>
       <c r="F49" s="99"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="32" t="s">
         <v>63</v>
       </c>
@@ -9743,6 +9751,7 @@
       <c r="F50" s="99"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -9751,22 +9760,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74AE8DF7-6359-F54D-8998-CBB487559808}">
   <dimension ref="A7:R50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="33.5" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.46484375" style="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" style="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="20.1328125" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1328125" style="26" customWidth="1"/>
     <col min="6" max="6" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.33203125" style="26" customWidth="1"/>
-    <col min="8" max="8" width="28.5" style="26" customWidth="1"/>
-    <col min="9" max="9" width="28.1640625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="28.46484375" style="26" customWidth="1"/>
+    <col min="9" max="9" width="28.1328125" style="26" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="26"/>
+    <col min="11" max="16384" width="10.796875" style="26"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:11" s="31" customFormat="1" ht="19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" s="31" customFormat="1" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A7" s="55" t="s">
         <v>14</v>
       </c>
@@ -9786,7 +9795,7 @@
       <c r="J7" s="26"/>
       <c r="K7" s="26"/>
     </row>
-    <row r="8" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="32" t="s">
         <v>7</v>
       </c>
@@ -9808,7 +9817,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="32" t="s">
         <v>8</v>
       </c>
@@ -9830,7 +9839,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="32" t="s">
         <v>9</v>
       </c>
@@ -9852,7 +9861,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A11" s="32" t="s">
         <v>5</v>
       </c>
@@ -9865,7 +9874,6 @@
         <v>500000</v>
       </c>
       <c r="D11" s="32"/>
-      <c r="E11" s="114"/>
       <c r="H11" s="33" t="s">
         <v>43</v>
       </c>
@@ -9873,7 +9881,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -9885,7 +9893,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="34" t="s">
         <v>26</v>
       </c>
@@ -9901,7 +9909,7 @@
       <c r="J13" s="31"/>
       <c r="K13" s="31"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="41" t="s">
         <v>29</v>
       </c>
@@ -9919,7 +9927,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15" s="42" t="s">
         <v>30</v>
       </c>
@@ -9934,7 +9942,7 @@
         <v>0.10279500898504523</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="42" t="s">
         <v>27</v>
       </c>
@@ -9949,7 +9957,7 @@
         <v>57286.244511836332</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A17" s="35" t="s">
         <v>28</v>
       </c>
@@ -9965,12 +9973,12 @@
         <v>6.9824790123456788</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="22.3" x14ac:dyDescent="0.5">
       <c r="A19" s="81" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A20" s="30" t="s">
         <v>78</v>
       </c>
@@ -9994,7 +10002,7 @@
       <c r="Q20" s="31"/>
       <c r="R20" s="31"/>
     </row>
-    <row r="21" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="57" t="s">
         <v>20</v>
       </c>
@@ -10025,7 +10033,7 @@
       <c r="Q21" s="31"/>
       <c r="R21" s="31"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A22" s="33" t="s">
         <v>32</v>
       </c>
@@ -10057,7 +10065,7 @@
       <c r="Q22" s="31"/>
       <c r="R22" s="31"/>
     </row>
-    <row r="23" spans="1:18" ht="51" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" ht="46.3" x14ac:dyDescent="0.4">
       <c r="A23" s="37" t="s">
         <v>21</v>
       </c>
@@ -10088,7 +10096,7 @@
       <c r="Q23" s="31"/>
       <c r="R23" s="31"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A24" s="33" t="s">
         <v>31</v>
       </c>
@@ -10119,7 +10127,7 @@
       <c r="Q24" s="31"/>
       <c r="R24" s="31"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A25" s="33" t="s">
         <v>33</v>
       </c>
@@ -10151,7 +10159,7 @@
       <c r="Q25" s="31"/>
       <c r="R25" s="31"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A26" s="33" t="s">
         <v>34</v>
       </c>
@@ -10173,7 +10181,7 @@
         <v>29989050.000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A27" s="78" t="s">
         <v>76</v>
       </c>
@@ -10183,7 +10191,7 @@
       <c r="C27" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="D27" s="115">
+      <c r="D27" s="114">
         <v>0.1251717032967033</v>
       </c>
       <c r="E27" s="75">
@@ -10195,7 +10203,7 @@
         <v>0.32955000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
         <v>77</v>
       </c>
@@ -10203,7 +10211,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="88"/>
-      <c r="D28" s="116">
+      <c r="D28" s="115">
         <v>0.11265453296703297</v>
       </c>
       <c r="E28" s="73">
@@ -10215,7 +10223,7 @@
         <v>0.29659500000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A29" s="29" t="s">
         <v>39</v>
       </c>
@@ -10225,7 +10233,7 @@
       <c r="C29" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="D29" s="116">
+      <c r="D29" s="115">
         <v>0.53106593406593405</v>
       </c>
       <c r="E29" s="73">
@@ -10237,7 +10245,7 @@
         <v>0.77482829670329667</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A30" s="78" t="s">
         <v>40</v>
       </c>
@@ -10248,7 +10256,7 @@
         <f>I15</f>
         <v>0.10279500898504523</v>
       </c>
-      <c r="D30" s="115">
+      <c r="D30" s="114">
         <v>0.23569898814327395</v>
       </c>
       <c r="E30" s="103">
@@ -10260,7 +10268,7 @@
         <v>0.42532003722909195</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
         <v>55</v>
       </c>
@@ -10271,7 +10279,7 @@
       <c r="C31" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="D31" s="117">
+      <c r="D31" s="116">
         <v>154192.51347756785</v>
       </c>
       <c r="E31" s="71">
@@ -10286,7 +10294,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A32" s="29" t="s">
         <v>57</v>
       </c>
@@ -10297,7 +10305,7 @@
       <c r="C32" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="D32" s="118">
+      <c r="D32" s="117">
         <v>9.7280987654320992</v>
       </c>
       <c r="E32" s="43">
@@ -10309,7 +10317,7 @@
         <v>1.537457007951522</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33" s="78" t="s">
         <v>56</v>
       </c>
@@ -10321,7 +10329,7 @@
         <f>I16</f>
         <v>57286.244511836332</v>
       </c>
-      <c r="D33" s="119">
+      <c r="D33" s="118">
         <v>171858.733535509</v>
       </c>
       <c r="E33" s="76">
@@ -10334,7 +10342,7 @@
       </c>
       <c r="H33" s="27"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34" s="78" t="s">
         <v>58</v>
       </c>
@@ -10346,7 +10354,7 @@
         <f>C22/C33</f>
         <v>6.9824790123456788</v>
       </c>
-      <c r="D34" s="120">
+      <c r="D34" s="119">
         <v>8.7280987654320974</v>
       </c>
       <c r="E34" s="77">
@@ -10359,7 +10367,7 @@
       </c>
       <c r="H34" s="27"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35" s="78" t="s">
         <v>38</v>
       </c>
@@ -10371,7 +10379,7 @@
         <f>I14</f>
         <v>3891239.5061728396</v>
       </c>
-      <c r="D35" s="120">
+      <c r="D35" s="119">
         <v>6364049.3827160494</v>
       </c>
       <c r="E35" s="77">
@@ -10383,7 +10391,7 @@
         <v>24687292.111620735</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36" s="78" t="s">
         <v>37</v>
       </c>
@@ -10395,7 +10403,7 @@
         <f>C35-C22</f>
         <v>3491239.5061728396</v>
       </c>
-      <c r="D36" s="120">
+      <c r="D36" s="119">
         <v>4864049.3827160494</v>
       </c>
       <c r="E36" s="77">
@@ -10407,7 +10415,7 @@
         <v>14187292.111620735</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39" s="29" t="s">
         <v>61</v>
       </c>
@@ -10416,7 +10424,7 @@
         <v>19885489.461418498</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40" s="29" t="s">
         <v>59</v>
       </c>
@@ -10425,7 +10433,7 @@
         <v>4.5762011629915733</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41" s="29" t="s">
         <v>60</v>
       </c>
@@ -10445,17 +10453,17 @@
         <v>0.34959236129565907</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44" s="34" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45" s="26" t="s">
         <v>67</v>
       </c>
@@ -10463,7 +10471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A46" s="55" t="s">
         <v>66</v>
       </c>
@@ -10482,7 +10490,7 @@
       <c r="F46" s="98"/>
       <c r="K46" s="44"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A47" s="32" t="s">
         <v>7</v>
       </c>
@@ -10502,7 +10510,7 @@
       </c>
       <c r="F47" s="99"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A48" s="32" t="s">
         <v>8</v>
       </c>
@@ -10525,7 +10533,7 @@
         <v>686430.17444873601</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="32" t="s">
         <v>9</v>
       </c>
@@ -10545,7 +10553,7 @@
       </c>
       <c r="F49" s="99"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="32" t="s">
         <v>63</v>
       </c>
@@ -10567,6 +10575,7 @@
       <c r="F50" s="99"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -10575,21 +10584,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8CF2466-F5A6-BC43-880B-4D266B791597}">
   <dimension ref="A7:Q53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="33.5" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.46484375" style="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" style="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1328125" style="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.33203125" style="26" customWidth="1"/>
-    <col min="7" max="7" width="28.5" style="26" customWidth="1"/>
-    <col min="8" max="8" width="28.1640625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="28.46484375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="28.1328125" style="26" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="26"/>
+    <col min="10" max="16384" width="10.796875" style="26"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:10" s="31" customFormat="1" ht="19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" s="31" customFormat="1" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A7" s="55" t="s">
         <v>14</v>
       </c>
@@ -10608,7 +10617,7 @@
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
     </row>
-    <row r="8" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="32" t="s">
         <v>7</v>
       </c>
@@ -10629,7 +10638,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="32" t="s">
         <v>8</v>
       </c>
@@ -10650,7 +10659,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="32" t="s">
         <v>9</v>
       </c>
@@ -10671,7 +10680,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A11" s="32" t="s">
         <v>5</v>
       </c>
@@ -10691,7 +10700,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
       <c r="G12" s="33" t="s">
@@ -10702,7 +10711,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="34" t="s">
         <v>26</v>
       </c>
@@ -10718,7 +10727,7 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="41" t="s">
         <v>29</v>
       </c>
@@ -10736,7 +10745,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="42" t="s">
         <v>30</v>
       </c>
@@ -10751,7 +10760,7 @@
         <v>1.3217348471530534</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="42" t="s">
         <v>27</v>
       </c>
@@ -10766,7 +10775,7 @@
         <v>-2054074.7432998563</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="35" t="s">
         <v>28</v>
       </c>
@@ -10782,7 +10791,7 @@
         <v>-0.19473488065843353</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="22.3" x14ac:dyDescent="0.5">
       <c r="A19" s="81" t="s">
         <v>87</v>
       </c>
@@ -10790,7 +10799,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A20" s="30" t="s">
         <v>78</v>
       </c>
@@ -10813,7 +10822,7 @@
       <c r="P20" s="31"/>
       <c r="Q20" s="31"/>
     </row>
-    <row r="21" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="57" t="s">
         <v>81</v>
       </c>
@@ -10844,7 +10853,7 @@
       <c r="P21" s="31"/>
       <c r="Q21" s="31"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="33" t="s">
         <v>32</v>
       </c>
@@ -10876,7 +10885,7 @@
       <c r="P22" s="31"/>
       <c r="Q22" s="31"/>
     </row>
-    <row r="23" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="46.3" x14ac:dyDescent="0.4">
       <c r="A23" s="37" t="s">
         <v>21</v>
       </c>
@@ -10907,7 +10916,7 @@
       <c r="P23" s="31"/>
       <c r="Q23" s="31"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="33" t="s">
         <v>31</v>
       </c>
@@ -10938,7 +10947,7 @@
       <c r="P24" s="31"/>
       <c r="Q24" s="31"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A25" s="33" t="s">
         <v>33</v>
       </c>
@@ -10972,7 +10981,7 @@
       <c r="P25" s="31"/>
       <c r="Q25" s="31"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="33" t="s">
         <v>34</v>
       </c>
@@ -10995,7 +11004,7 @@
         <v>29989050.000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="78" t="s">
         <v>76</v>
       </c>
@@ -11018,7 +11027,7 @@
         <v>0.32955000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
         <v>77</v>
       </c>
@@ -11039,7 +11048,7 @@
         <v>0.29659500000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="29" t="s">
         <v>39</v>
       </c>
@@ -11062,7 +11071,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="78" t="s">
         <v>40</v>
       </c>
@@ -11086,7 +11095,7 @@
         <v>0.36616666666666675</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
         <v>55</v>
       </c>
@@ -11113,7 +11122,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="29"/>
       <c r="B32" s="95"/>
       <c r="D32" s="108">
@@ -11127,7 +11136,7 @@
       </c>
       <c r="G32" s="27"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="29" t="s">
         <v>57</v>
       </c>
@@ -11151,7 +11160,7 @@
         <v>2.0115857287910166</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="29"/>
       <c r="B34" s="28"/>
       <c r="C34" s="90"/>
@@ -11165,7 +11174,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="78" t="s">
         <v>56</v>
       </c>
@@ -11191,7 +11200,7 @@
       </c>
       <c r="G35" s="27"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="78" t="s">
         <v>58</v>
       </c>
@@ -11217,7 +11226,7 @@
       </c>
       <c r="G36" s="27"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="78" t="s">
         <v>38</v>
       </c>
@@ -11242,7 +11251,7 @@
         <v>28675466.545289025</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="78"/>
       <c r="B38" s="94"/>
       <c r="C38" s="93"/>
@@ -11256,7 +11265,7 @@
         <v>28675000</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="78" t="s">
         <v>37</v>
       </c>
@@ -11281,7 +11290,7 @@
         <v>18175466.545289025</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D40" s="111">
         <v>4864000</v>
       </c>
@@ -11292,7 +11301,7 @@
         <v>18175000</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="29" t="s">
         <v>61</v>
       </c>
@@ -11301,7 +11310,7 @@
         <v>-49230169.979334854</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="29" t="s">
         <v>59</v>
       </c>
@@ -11310,7 +11319,7 @@
         <v>-1.8484599999999736</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="29" t="s">
         <v>60</v>
       </c>
@@ -11329,7 +11338,7 @@
         <v>0.30000000000000004</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" s="27" t="s">
         <v>62</v>
       </c>
@@ -11343,12 +11352,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="34" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="26" t="s">
         <v>84</v>
       </c>
@@ -11357,7 +11366,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A49" s="55" t="s">
         <v>66</v>
       </c>
@@ -11376,7 +11385,7 @@
       <c r="F49" s="98"/>
       <c r="J49" s="44"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A50" s="32" t="s">
         <v>7</v>
       </c>
@@ -11401,7 +11410,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A51" s="32" t="s">
         <v>8</v>
       </c>
@@ -11426,7 +11435,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A52" s="32" t="s">
         <v>9</v>
       </c>
@@ -11451,7 +11460,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A53" s="32" t="s">
         <v>63</v>
       </c>
@@ -11473,6 +11482,7 @@
       <c r="F53" s="27"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -11481,21 +11491,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC9CD10-D0E0-D541-9942-9803788B9832}">
   <dimension ref="A7:Q56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.45" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="35.5" style="26" customWidth="1"/>
+    <col min="1" max="1" width="35.46484375" style="26" customWidth="1"/>
     <col min="2" max="2" width="21.6640625" style="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1328125" style="26" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" style="26" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.33203125" style="26" customWidth="1"/>
-    <col min="7" max="7" width="28.5" style="26" customWidth="1"/>
-    <col min="8" max="8" width="28.1640625" style="26" customWidth="1"/>
+    <col min="7" max="7" width="28.46484375" style="26" customWidth="1"/>
+    <col min="8" max="8" width="28.1328125" style="26" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="26"/>
+    <col min="10" max="16384" width="10.796875" style="26"/>
   </cols>
   <sheetData>
-    <row r="7" spans="1:10" s="31" customFormat="1" ht="19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" s="31" customFormat="1" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A7" s="55" t="s">
         <v>14</v>
       </c>
@@ -11514,7 +11524,7 @@
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
     </row>
-    <row r="8" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="32" t="s">
         <v>7</v>
       </c>
@@ -11535,7 +11545,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="32" t="s">
         <v>8</v>
       </c>
@@ -11556,7 +11566,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="32" t="s">
         <v>9</v>
       </c>
@@ -11577,7 +11587,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A11" s="32" t="s">
         <v>5</v>
       </c>
@@ -11597,7 +11607,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3"/>
       <c r="D12" s="4"/>
       <c r="G12" s="33" t="s">
@@ -11608,7 +11618,7 @@
         <v>YES</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="34" t="s">
         <v>26</v>
       </c>
@@ -11624,7 +11634,7 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="41" t="s">
         <v>29</v>
       </c>
@@ -11642,7 +11652,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="42" t="s">
         <v>30</v>
       </c>
@@ -11657,7 +11667,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="42" t="s">
         <v>27</v>
       </c>
@@ -11672,7 +11682,7 @@
         <v>55555.555555555562</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" s="35" t="s">
         <v>28</v>
       </c>
@@ -11688,12 +11698,12 @@
         <v>7.1999999999999993</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="22.3" x14ac:dyDescent="0.5">
       <c r="A19" s="81" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A20" s="30" t="s">
         <v>78</v>
       </c>
@@ -11716,7 +11726,7 @@
       <c r="P20" s="31"/>
       <c r="Q20" s="31"/>
     </row>
-    <row r="21" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="57" t="s">
         <v>20</v>
       </c>
@@ -11747,7 +11757,7 @@
       <c r="P21" s="31"/>
       <c r="Q21" s="31"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" s="33" t="s">
         <v>32</v>
       </c>
@@ -11779,7 +11789,7 @@
       <c r="P22" s="31"/>
       <c r="Q22" s="31"/>
     </row>
-    <row r="23" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="46.3" x14ac:dyDescent="0.4">
       <c r="A23" s="37" t="s">
         <v>21</v>
       </c>
@@ -11810,7 +11820,7 @@
       <c r="P23" s="31"/>
       <c r="Q23" s="31"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" s="33" t="s">
         <v>31</v>
       </c>
@@ -11841,7 +11851,7 @@
       <c r="P24" s="31"/>
       <c r="Q24" s="31"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A25" s="33" t="s">
         <v>33</v>
       </c>
@@ -11873,7 +11883,7 @@
       <c r="P25" s="31"/>
       <c r="Q25" s="31"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" s="33" t="s">
         <v>34</v>
       </c>
@@ -11896,7 +11906,7 @@
         <v>14365000.000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A27" s="78" t="s">
         <v>76</v>
       </c>
@@ -11919,7 +11929,7 @@
         <v>0.15785714285714289</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
         <v>77</v>
       </c>
@@ -11940,7 +11950,7 @@
         <v>0.1420714285714286</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A29" s="29" t="s">
         <v>39</v>
       </c>
@@ -11963,7 +11973,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A30" s="78" t="s">
         <v>40</v>
       </c>
@@ -11987,7 +11997,7 @@
         <v>0.15785714285714289</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A31" s="29" t="s">
         <v>55</v>
       </c>
@@ -12014,7 +12024,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A32" s="29" t="s">
         <v>57</v>
       </c>
@@ -12038,7 +12048,7 @@
         <v>53.163512429920416</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A33" s="78" t="s">
         <v>56</v>
       </c>
@@ -12064,7 +12074,7 @@
       </c>
       <c r="G33" s="27"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A34" s="78" t="s">
         <v>58</v>
       </c>
@@ -12090,7 +12100,7 @@
       </c>
       <c r="G34" s="27"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A35" s="78" t="s">
         <v>38</v>
       </c>
@@ -12115,7 +12125,7 @@
         <v>53846153.846153833</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A36" s="78" t="s">
         <v>37</v>
       </c>
@@ -12140,7 +12150,7 @@
         <v>45346153.846153833</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A39" s="29" t="s">
         <v>61</v>
       </c>
@@ -12149,7 +12159,7 @@
         <v>1250420.2620364618</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A40" s="29" t="s">
         <v>59</v>
       </c>
@@ -12158,7 +12168,7 @@
         <v>72.775532165318083</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A41" s="29" t="s">
         <v>86</v>
       </c>
@@ -12167,7 +12177,7 @@
         <v>60.379699763533139</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A42" s="29" t="s">
         <v>60</v>
       </c>
@@ -12186,17 +12196,17 @@
       </c>
       <c r="F42" s="84"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A43" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A45" s="34" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A46" s="26" t="s">
         <v>67</v>
       </c>
@@ -12205,7 +12215,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="18.899999999999999" x14ac:dyDescent="0.8">
       <c r="A47" s="55" t="s">
         <v>66</v>
       </c>
@@ -12224,7 +12234,7 @@
       <c r="F47" s="98"/>
       <c r="J47" s="44"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A48" s="32" t="s">
         <v>7</v>
       </c>
@@ -12244,7 +12254,7 @@
       </c>
       <c r="F48" s="99"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="32" t="s">
         <v>8</v>
       </c>
@@ -12264,7 +12274,7 @@
       </c>
       <c r="F49" s="99"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="32" t="s">
         <v>9</v>
       </c>
@@ -12284,7 +12294,7 @@
       </c>
       <c r="F50" s="99"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" s="32" t="s">
         <v>63</v>
       </c>
@@ -12305,11 +12315,11 @@
       </c>
       <c r="F51" s="99"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="D52" s="102"/>
       <c r="E52" s="99"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" s="26" t="s">
         <v>85</v>
       </c>
@@ -12320,7 +12330,7 @@
       <c r="D53" s="102"/>
       <c r="E53" s="99"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" s="28" t="s">
         <v>4</v>
       </c>
@@ -12341,7 +12351,7 @@
         <v>0.43197181276406549</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55" s="28" t="s">
         <v>82</v>
       </c>
@@ -12362,7 +12372,7 @@
         <v>0.45692855607598304</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56" s="28" t="s">
         <v>83</v>
       </c>
@@ -12384,6 +12394,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
